--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,6 +880,209 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129362047</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105751</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567715</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6507329</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129362908</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91507</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567640</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6507275</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105751</v>
+        <v>105767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91507</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342896</v>
       </c>
       <c r="B2" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349184</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129362047</v>
       </c>
       <c r="B4" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129362908</v>
       </c>
       <c r="B5" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129342896</v>
+        <v>129342590</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567596</v>
+        <v>567580</v>
       </c>
       <c r="R2" t="n">
-        <v>6507317</v>
+        <v>6507354</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -772,60 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129349184</v>
+        <v>129342522</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Branten SV om Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567599</v>
+        <v>567580</v>
       </c>
       <c r="R3" t="n">
-        <v>6507287</v>
+        <v>6507354</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,29 +851,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129362047</v>
+        <v>129362908</v>
       </c>
       <c r="B4" t="n">
-        <v>105840</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,46 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567715</v>
+        <v>567640</v>
       </c>
       <c r="R4" t="n">
-        <v>6507329</v>
+        <v>6507275</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129362908</v>
+        <v>129342896</v>
       </c>
       <c r="B5" t="n">
-        <v>91557</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567640</v>
+        <v>567596</v>
       </c>
       <c r="R5" t="n">
-        <v>6507275</v>
+        <v>6507317</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1053,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,6 +1060,222 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129349184</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Branten SV om Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>567599</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6507287</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129362047</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567715</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6507329</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44700-2025 artfynd.xlsx
+++ b/artfynd/A 44700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129342590</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129342522</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129362908</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129342896</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129349184</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,8 +1306,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129362047</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>